--- a/Result/profitability/6506.xlsx
+++ b/Result/profitability/6506.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2612499999999999</v>
+        <v>0.3337499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>14.91875</v>
+        <v>15.83375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>97.2</v>
@@ -780,10 +780,10 @@
         <v>-0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0.26</v>
+        <v>0.2874999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>14.44625</v>
+        <v>15.90625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4037499999999999</v>
+        <v>0.4049999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>15.43625</v>
+        <v>15.73625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3599999999999999</v>
+        <v>0.4012499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>14.73375</v>
+        <v>15.35625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.36625</v>
+        <v>0.39</v>
       </c>
       <c r="N6" t="n">
-        <v>14.7625</v>
+        <v>15.43125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.35375</v>
+        <v>0.3674999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>14.5675</v>
+        <v>15.17625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.4275</v>
       </c>
       <c r="N8" t="n">
-        <v>15.1525</v>
+        <v>15.14</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.17</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3962499999999999</v>
+        <v>0.39625</v>
       </c>
       <c r="N9" t="n">
         <v>14.2075</v>
@@ -1645,7 +1645,7 @@
         <v>0.03</v>
       </c>
       <c r="M10" t="n">
-        <v>0.33875</v>
+        <v>0.3387499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>13.82375</v>
@@ -9449,6 +9449,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>6506</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>546</v>
+      </c>
+      <c r="D72" t="n">
+        <v>435</v>
+      </c>
+      <c r="E72" t="n">
+        <v>111</v>
+      </c>
+      <c r="F72" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="G72" t="n">
+        <v>60</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>10.91%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>58</v>
+      </c>
+      <c r="K72" t="n">
+        <v>35</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.2524999999999999</v>
+      </c>
+      <c r="N72" t="n">
+        <v>15.7775</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-0.1923076923076924</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>-0.1000000000000014</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>-0.004892367906066619</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.32421875</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
